--- a/data/trans_dic/P1419-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1419-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,98</t>
+          <t>0,5; 2,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,91</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,51</t>
+          <t>0,28; 1,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,27 +824,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>1,23%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -857,52 +857,52 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,33</t>
+          <t>0,5; 2,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,19</t>
+          <t>0,14; 1,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 0,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,38; 7,17</t>
+          <t>3,36; 6,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,35</t>
+          <t>0,47; 2,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,67</t>
+          <t>0,19; 1,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,58</t>
+          <t>0,96; 3,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,99</t>
+          <t>2,05; 4,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,32</t>
+          <t>0,38; 1,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,79</t>
+          <t>0,63; 2,12</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,74</t>
+          <t>0,75; 2,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,34</t>
+          <t>0,27; 2,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,79</t>
+          <t>1,2; 3,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,51; 9,32</t>
+          <t>5,45; 9,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,63</t>
+          <t>3,98; 7,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,18</t>
+          <t>1,01; 3,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,02</t>
+          <t>4,74; 8,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 5,74</t>
+          <t>3,47; 5,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,52</t>
+          <t>2,32; 4,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,7</t>
+          <t>0,57; 1,67</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,31</t>
+          <t>3,25; 5,52</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,08</t>
+          <t>2,41; 6,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,21</t>
+          <t>0,73; 3,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,67</t>
+          <t>1,76; 4,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,23</t>
+          <t>2,34; 5,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,14; 13,29</t>
+          <t>8,03; 13,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,94</t>
+          <t>4,77; 9,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,01; 7,8</t>
+          <t>4,11; 8,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,04; 14,31</t>
+          <t>10,5; 14,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,66; 9,08</t>
+          <t>5,76; 9,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,43</t>
+          <t>2,95; 5,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,58</t>
+          <t>3,08; 5,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 8,62</t>
+          <t>6,8; 9,34</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,56; 8,37</t>
+          <t>3,7; 8,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,74</t>
+          <t>0,48; 2,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,02</t>
+          <t>1,07; 4,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,24; 9,06</t>
+          <t>5,22; 9,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,13; 19,1</t>
+          <t>11,93; 18,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,37; 16,93</t>
+          <t>10,22; 16,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,02; 12,61</t>
+          <t>7,13; 12,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,34; 15,57</t>
+          <t>11,63; 16,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,77; 12,97</t>
+          <t>8,54; 12,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,5; 9,32</t>
+          <t>5,81; 9,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 7,61</t>
+          <t>4,46; 7,72</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,71; 11,7</t>
+          <t>8,79; 11,78</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,09; 9,83</t>
+          <t>4,13; 10,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,43</t>
+          <t>1,33; 5,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,72</t>
+          <t>1,54; 5,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,29</t>
+          <t>4,3; 8,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,37; 26,91</t>
+          <t>18,09; 26,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,21; 19,79</t>
+          <t>12,06; 19,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,99; 18,6</t>
+          <t>10,87; 18,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,61; 16,34</t>
+          <t>13,24; 18,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,67; 17,91</t>
+          <t>12,5; 17,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,68; 12,35</t>
+          <t>7,84; 12,33</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,0; 11,4</t>
+          <t>6,92; 11,37</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,12; 11,43</t>
+          <t>9,5; 12,62</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,39; 13,1</t>
+          <t>5,29; 13,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,15</t>
+          <t>1,35; 6,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,52</t>
+          <t>2,29; 7,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,09; 11,64</t>
+          <t>6,35; 12,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,18; 30,21</t>
+          <t>20,22; 30,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,7; 29,84</t>
+          <t>20,65; 29,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,04; 20,15</t>
+          <t>11,64; 20,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20,79; 26,61</t>
+          <t>20,77; 26,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,61; 22,6</t>
+          <t>15,74; 22,48</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13,49; 19,92</t>
+          <t>13,49; 19,85</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,66; 14,36</t>
+          <t>8,87; 14,48</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,47; 19,99</t>
+          <t>15,74; 19,97</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,64</t>
+          <t>2,44; 3,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,64</t>
+          <t>0,85; 1,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,97</t>
+          <t>1,15; 2,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,21</t>
+          <t>3,26; 4,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,8; 11,92</t>
+          <t>9,68; 11,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,55; 9,48</t>
+          <t>7,55; 9,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,29; 7,08</t>
+          <t>5,34; 7,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,23; 11,15</t>
+          <t>10,17; 11,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,37; 7,6</t>
+          <t>6,3; 7,57</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,32; 5,39</t>
+          <t>4,39; 5,43</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,44; 4,43</t>
+          <t>3,4; 4,4</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,03; 7,57</t>
+          <t>6,91; 7,97</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4764</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2350; 13944</t>
+          <t>2332; 13356</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 15385</t>
+          <t>0; 17009</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2396; 14521</t>
+          <t>2694; 13559</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 18519</t>
+          <t>0; 18510</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>9536</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>11988</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3519; 17111</t>
+          <t>3676; 17229</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>945; 8146</t>
+          <t>938; 7529</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5278</t>
+          <t>0; 5288</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 8074</t>
+          <t>0; 8533</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21113; 44819</t>
+          <t>21022; 43188</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2929; 14363</t>
+          <t>2880; 13903</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>940; 9434</t>
+          <t>1089; 9536</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2239; 13215</t>
+          <t>4794; 17104</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27925; 54364</t>
+          <t>27902; 54804</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4930; 17119</t>
+          <t>4959; 17959</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1844; 10973</t>
+          <t>1849; 10999</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3958; 16707</t>
+          <t>6130; 20728</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11087</t>
+          <t>13162</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33156</t>
+          <t>39238</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44243</t>
+          <t>52400</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5328; 17506</t>
+          <t>4811; 18816</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1890; 15953</t>
+          <t>1870; 15330</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7603</t>
+          <t>0; 7567</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5274; 20350</t>
+          <t>7460; 23741</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>37971; 64260</t>
+          <t>37609; 66433</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28528; 54133</t>
+          <t>28238; 54797</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6808; 21042</t>
+          <t>6658; 20150</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24277; 43469</t>
+          <t>29441; 49740</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46267; 76247</t>
+          <t>46057; 77913</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32948; 62841</t>
+          <t>32315; 62269</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8014; 22592</t>
+          <t>7648; 22276</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33216; 57302</t>
+          <t>40351; 68574</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23049</t>
+          <t>25759</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>86483</t>
+          <t>91124</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>109532</t>
+          <t>116883</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12853; 31576</t>
+          <t>12503; 32184</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4464; 19737</t>
+          <t>4505; 19284</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10677; 30161</t>
+          <t>11384; 29505</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8740; 37588</t>
+          <t>16363; 38335</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41969; 68541</t>
+          <t>41385; 69578</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28454; 54890</t>
+          <t>29321; 55564</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26045; 50630</t>
+          <t>26701; 52288</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>71489; 101838</t>
+          <t>77264; 106837</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>58531; 93991</t>
+          <t>59568; 93634</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36845; 66715</t>
+          <t>36225; 66097</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42742; 72319</t>
+          <t>39828; 72072</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>61832; 137805</t>
+          <t>97719; 134097</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38928</t>
+          <t>41896</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>73160</t>
+          <t>82367</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>112087</t>
+          <t>124263</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13749; 32356</t>
+          <t>14323; 31531</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2047; 11777</t>
+          <t>2048; 11592</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4989; 19194</t>
+          <t>5127; 19320</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29338; 50765</t>
+          <t>31750; 55148</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>49019; 77177</t>
+          <t>48186; 76670</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46439; 75813</t>
+          <t>45752; 74429</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34895; 62635</t>
+          <t>35441; 62867</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>61762; 84830</t>
+          <t>70562; 97318</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>69316; 102552</t>
+          <t>67540; 102121</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>48226; 81776</t>
+          <t>50931; 81999</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44576; 74186</t>
+          <t>43470; 75224</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>96291; 129257</t>
+          <t>106802; 143189</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21684</t>
+          <t>24420</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>62603</t>
+          <t>69080</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>84286</t>
+          <t>93501</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11961; 28747</t>
+          <t>12078; 29280</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4018; 16816</t>
+          <t>4123; 15960</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5613; 19137</t>
+          <t>5154; 17961</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15114; 30479</t>
+          <t>17466; 33877</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>62989; 92277</t>
+          <t>62045; 91442</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>43208; 70052</t>
+          <t>42692; 70437</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41534; 70281</t>
+          <t>41055; 70576</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>28023; 99415</t>
+          <t>58143; 80231</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>80536; 113798</t>
+          <t>79447; 113477</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>50961; 81998</t>
+          <t>52067; 81817</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49823; 81209</t>
+          <t>49308; 80999</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>40166; 111550</t>
+          <t>80270; 106683</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24774</t>
+          <t>27569</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>100334</t>
+          <t>110226</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>125108</t>
+          <t>137795</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11322; 27505</t>
+          <t>11097; 28104</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3513; 15361</t>
+          <t>3380; 15914</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5923; 19332</t>
+          <t>5894; 18286</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17234; 32901</t>
+          <t>19692; 37446</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>67394; 100881</t>
+          <t>67517; 102902</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>80521; 116079</t>
+          <t>80325; 115219</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48176; 80647</t>
+          <t>46566; 81592</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>88542; 113299</t>
+          <t>96517; 125227</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>84881; 122889</t>
+          <t>85605; 122236</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>86168; 127247</t>
+          <t>86163; 126800</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>56924; 94370</t>
+          <t>58300; 95157</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>109600; 141643</t>
+          <t>121965; 154718</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>121874</t>
+          <t>135259</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>366375</t>
+          <t>406336</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>488249</t>
+          <t>541595</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>80228; 119234</t>
+          <t>79996; 120579</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>28211; 56092</t>
+          <t>29023; 57158</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>39723; 66907</t>
+          <t>39141; 69582</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>93768; 145705</t>
+          <t>115239; 157044</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>331117; 402712</t>
+          <t>326983; 400540</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>268434; 337083</t>
+          <t>268396; 331839</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>187489; 251019</t>
+          <t>189281; 249845</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>301167; 407814</t>
+          <t>379438; 439184</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>424119; 505612</t>
+          <t>419464; 503578</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>301477; 376641</t>
+          <t>306249; 379222</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>238950; 307574</t>
+          <t>235967; 305143</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>428811; 538558</t>
+          <t>501568; 578599</t>
         </is>
       </c>
     </row>
